--- a/PaymentUsingWallet.xlsx
+++ b/PaymentUsingWallet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B0F582-98CD-4FBA-8C25-18FC009EE3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C15DFB5-C729-4236-B3CD-2FE139C9F0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3945" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PaymentUsingWallet" sheetId="1" r:id="rId1"/>
@@ -11294,7 +11294,7 @@
   <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
@@ -11423,7 +11423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>417</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>419</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>420</v>
       </c>
@@ -11593,7 +11593,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>421</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
